--- a/ALL/p11-out/START.xlsx
+++ b/ALL/p11-out/START.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Titles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Titles" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB4"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,71 +437,11 @@
           <t>used_project</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Column_5</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Column_6</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Column_7</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Column_8</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Column_9</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Column_10</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Column_11</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Column_12</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Column_13</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Column_14</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Column_15</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Column_16</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Creamy Garlic Chicken Pasta</t>
+          <t>Creamy Garlic Parmesan Chicken Pasta</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -509,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-30 09:07:34</t>
+          <t>2026-05-08 14:43:31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -521,7 +461,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spicy Honey Glazed Salmon</t>
+          <t>The Best Homemade Mac and Cheese</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -529,7 +469,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-30 07:13:13</t>
+          <t>2026-05-08 14:43:31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -541,20 +481,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pizza</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-04-30 07:13:13</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New site (p11)</t>
+          <t>Easy 15-Minute Beef Stir Fry</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cheesy Loaded Potato Soup</t>
         </is>
       </c>
     </row>

--- a/ALL/p11-out/START.xlsx
+++ b/ALL/p11-out/START.xlsx
@@ -484,11 +484,37 @@
           <t>Easy 15-Minute Beef Stir Fry</t>
         </is>
       </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-08 21:36:19</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New site (p11)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>Cheesy Loaded Potato Soup</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-05-08 21:36:19</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New site (p11)</t>
         </is>
       </c>
     </row>
